--- a/InputData/indst/_cement/CRBW/Cement Replacement Blend Weight vs Tightness.xlsx
+++ b/InputData/indst/_cement/CRBW/Cement Replacement Blend Weight vs Tightness.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CRBW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DED979F-43E6-429A-A408-1DC5EB12EE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55261DC0-782D-498C-B05A-C2F2573FFC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
     <t>tau</t>
   </si>
   <si>
-    <t>w(tau) = tau^p / (tau^p + k (1-tau)^p), rounded to 4 decimals</t>
-  </si>
-  <si>
     <t>Cement Replacement Blend Weight</t>
   </si>
   <si>
@@ -146,35 +143,38 @@
     <t>Purpose and layout</t>
   </si>
   <si>
+    <t>Using it for other regions</t>
+  </si>
+  <si>
+    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country, and the 'CRBWvT' tab updates on its own; just re-export the CSV. Every non-US row currently holds the template values (p = 2, k = 1) and is marked UNCALIBRATED. Those are placeholders, not results. To calibrate a region, solve for k so that the weight at the region's start-year tightness equals the build-new share that region's no-policy run should show (see the U.S. note), and enter it on the 'Regions' tab. Tightness itself needs that region's CULB, CUUB, and start-year utilization.</t>
+  </si>
+  <si>
+    <t>U.S. values</t>
+  </si>
+  <si>
+    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
+  </si>
+  <si>
+    <t>CALIBRATED</t>
+  </si>
+  <si>
+    <t>k solved so the curve reproduces the start-year overhaul-or-replace mix (see About notes)</t>
+  </si>
+  <si>
+    <t>k = 1.0 is a template, not a value: solve k from the region's start-year tightness and calibrated overhaul share, as was done for the US (see About notes).</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>w(tau) = tau^p / (tau^p + k (1-tau)^p)</t>
+  </si>
+  <si>
     <t>When a kiln reaches the end of a campaign, EPS compares the cost of overhauling it with the cost of retiring it and replacing the output. The cost of the retire alternative is a blend of two things: what it costs the rest of the fleet to absorb the lost output (just the operating cost, since the capital is already sunk) and what it costs to build new capacity. This file gives the weight on the build-new cost as a function of 'fleet tightness', which runs from 0 (utilization at the bottom of the region's historical range, CULB) to 1 (at the top, CUUB). In a slack market the weight is near 0 because other kilns can pick up the output; in a tight market it is near 1 because new capacity is needed.
-The curve is w = tau^p / (tau^p + k x (1 - tau)^p), with tightness written as tau. It is exactly 0 at tau = 0 and exactly 1 at tau = 1. p sets how steep the S-curve is, and k shifts its midpoint (p = 1 and k = 1 is a straight line). The tabs are 'Regions' (p and k for each region), 'Derivation' (samples the curve at 21 points, tau = 0 to 1 in steps of 0.05, rounded to four decimals), and the last tab, 'CRBWvT', which reads the Derivation and is exported to CRBWvT.csv. This file has no outside data tab; it is a calibrated curve. The curve is the same for every kiln pathway.</t>
-  </si>
-  <si>
-    <t>Using it for other regions</t>
-  </si>
-  <si>
-    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country, and the 'CRBWvT' tab updates on its own; just re-export the CSV. Every non-US row currently holds the template values (p = 2, k = 1) and is marked UNCALIBRATED. Those are placeholders, not results. To calibrate a region, solve for k so that the weight at the region's start-year tightness equals the build-new share that region's no-policy run should show (see the U.S. note), and enter it on the 'Regions' tab. Tightness itself needs that region's CULB, CUUB, and start-year utilization.</t>
-  </si>
-  <si>
-    <t>U.S. values</t>
-  </si>
-  <si>
-    <t>For the U.S. national file version, p = 2, our judgment for a gentle S-curve; running with p = 1 or 3 made little difference. k = 0.3686 was solved so that at the U.S. start-year tightness (about 0.55, from the 2025 utilization of 0.69 inside the 0.49 to 0.85 range) the weight is 0.7964. That value is one minus the average share of retiring kiln output that the rest of the fleet could absorb over 2026-2035 in a no-policy run, so the BAU overhaul-or-replace mix matches the start-year calibration. Because k is rounded to four decimals in the workbook, the weights at tightness 0.40 and 0.65 come out 0.0001 below the shipped CSV (0.5466 and 0.9034 against 0.5467 and 0.9035); the difference does not matter.</t>
-  </si>
-  <si>
-    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
-  </si>
-  <si>
-    <t>CALIBRATED</t>
-  </si>
-  <si>
-    <t>k solved so the curve reproduces the start-year overhaul-or-replace mix (see About notes)</t>
-  </si>
-  <si>
-    <t>k = 1.0 is a template, not a value: solve k from the region's start-year tightness and calibrated overhaul share, as was done for the US (see About notes).</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
+The curve is w = tau^p / (tau^p + k x (1 - tau)^p), with tightness written as tau. It is exactly 0 at tau = 0 and exactly 1 at tau = 1. p sets how steep the S-curve is, and k shifts its midpoint (p = 1 and k = 1 is a straight line). The tabs are 'Regions' (p and k for each region), 'Derivation' (samples the curve at 21 points, tau = 0 to 1 in steps of 0.05), and the last tab, 'CRBWvT', which reads the Derivation and is exported to CRBWvT.csv. This file has no outside data tab; it is a calibrated curve. The curve is the same for every kiln pathway.</t>
+  </si>
+  <si>
+    <t>For the U.S. national file version, p = 2, our judgment for a gentle S-curve; running with p = 1 or 3 made little difference. k = 0.3686 was solved so that at the U.S. start-year tightness (about 0.55, from the 2025 utilization of 0.69 inside the 0.49 to 0.85 range) the weight is 0.7964. That value is one minus the average share of retiring kiln output that the rest of the fleet could absorb over 2026-2035 in a no-policy run, so the BAU overhaul-or-replace mix matches the start-year calibration.</t>
   </si>
 </sst>
 </file>
@@ -254,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -274,6 +274,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -580,112 +583,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="9">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="9"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B15" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="180" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+    <row r="21" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>40</v>
+      <c r="B21" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{18087965-76F6-495F-935A-403B672AB1CA}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{D8E37B77-E12B-4788-9207-01F4C59B8F19}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{767C7D1E-4D5D-497B-A3F8-559E7907E74E}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{103023CF-1AEB-4DB9-95E7-E164A3C694CF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -694,7 +698,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -703,7 +707,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -711,12 +715,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -733,7 +737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -744,13 +748,13 @@
         <v>0.36859999999999998</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -764,10 +768,10 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -781,10 +785,10 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -798,10 +802,10 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -815,10 +819,10 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -832,10 +836,10 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -849,10 +853,10 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -866,10 +870,10 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -883,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -900,7 +904,7 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -916,12 +920,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -930,7 +934,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -939,7 +943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -948,7 +952,7 @@
         <v>0.36859999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1016,89 +1020,89 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <f t="shared" ref="B6:V6" si="0">IF(B5&lt;=0,0,IF(B5&gt;=1,1,ROUND(B5^$B$2/(B5^$B$2+$B$3*(1-B5)^$B$2),4)))</f>
+        <f t="shared" ref="B6:V6" si="0">IF(B5&lt;=0,0,IF(B5&gt;=1,1,(B5^$B$2/(B5^$B$2+$B$3*(1-B5)^$B$2))))</f>
         <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>7.4999999999999997E-3</v>
+        <v>7.459090617508277E-3</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>3.2399999999999998E-2</v>
+        <v>3.240797754775316E-2</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>7.7899999999999997E-2</v>
+        <v>7.7904945579067464E-2</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>0.14499999999999999</v>
+        <v>0.14497796334957086</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0.2316</v>
+        <v>0.23162088293880581</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0.33260000000000001</v>
+        <v>0.33257702853510906</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0.44030000000000002</v>
+        <v>0.44027768043747428</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0.54659999999999997</v>
+        <v>0.54664224997950095</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.64490000000000003</v>
+        <v>0.64490137785965984</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0.73070000000000002</v>
+        <v>0.73067368113400555</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0.80210000000000004</v>
+        <v>0.80208621962844195</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>0.85919999999999996</v>
+        <v>0.85923776063545398</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.90339999999999998</v>
+        <v>0.90344667579735849</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>0.93659999999999999</v>
+        <v>0.93659088563269588</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>0.9607</v>
+        <v>0.96065580769805514</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>0.97750000000000004</v>
+        <v>0.97748127512432348</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>0.98870000000000002</v>
+        <v>0.98865137689374638</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>0.99550000000000005</v>
+        <v>0.99546999702587979</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>0.999</v>
+        <v>0.99897998885348638</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
@@ -1116,11 +1120,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -1186,9 +1190,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <f>Derivation!B6</f>
@@ -1196,79 +1200,79 @@
       </c>
       <c r="C2">
         <f>Derivation!C6</f>
-        <v>7.4999999999999997E-3</v>
+        <v>7.459090617508277E-3</v>
       </c>
       <c r="D2">
         <f>Derivation!D6</f>
-        <v>3.2399999999999998E-2</v>
+        <v>3.240797754775316E-2</v>
       </c>
       <c r="E2">
         <f>Derivation!E6</f>
-        <v>7.7899999999999997E-2</v>
+        <v>7.7904945579067464E-2</v>
       </c>
       <c r="F2">
         <f>Derivation!F6</f>
-        <v>0.14499999999999999</v>
+        <v>0.14497796334957086</v>
       </c>
       <c r="G2">
         <f>Derivation!G6</f>
-        <v>0.2316</v>
+        <v>0.23162088293880581</v>
       </c>
       <c r="H2">
         <f>Derivation!H6</f>
-        <v>0.33260000000000001</v>
+        <v>0.33257702853510906</v>
       </c>
       <c r="I2">
         <f>Derivation!I6</f>
-        <v>0.44030000000000002</v>
+        <v>0.44027768043747428</v>
       </c>
       <c r="J2">
         <f>Derivation!J6</f>
-        <v>0.54659999999999997</v>
+        <v>0.54664224997950095</v>
       </c>
       <c r="K2">
         <f>Derivation!K6</f>
-        <v>0.64490000000000003</v>
+        <v>0.64490137785965984</v>
       </c>
       <c r="L2">
         <f>Derivation!L6</f>
-        <v>0.73070000000000002</v>
+        <v>0.73067368113400555</v>
       </c>
       <c r="M2">
         <f>Derivation!M6</f>
-        <v>0.80210000000000004</v>
+        <v>0.80208621962844195</v>
       </c>
       <c r="N2">
         <f>Derivation!N6</f>
-        <v>0.85919999999999996</v>
+        <v>0.85923776063545398</v>
       </c>
       <c r="O2">
         <f>Derivation!O6</f>
-        <v>0.90339999999999998</v>
+        <v>0.90344667579735849</v>
       </c>
       <c r="P2">
         <f>Derivation!P6</f>
-        <v>0.93659999999999999</v>
+        <v>0.93659088563269588</v>
       </c>
       <c r="Q2">
         <f>Derivation!Q6</f>
-        <v>0.9607</v>
+        <v>0.96065580769805514</v>
       </c>
       <c r="R2">
         <f>Derivation!R6</f>
-        <v>0.97750000000000004</v>
+        <v>0.97748127512432348</v>
       </c>
       <c r="S2">
         <f>Derivation!S6</f>
-        <v>0.98870000000000002</v>
+        <v>0.98865137689374638</v>
       </c>
       <c r="T2">
         <f>Derivation!T6</f>
-        <v>0.99550000000000005</v>
+        <v>0.99546999702587979</v>
       </c>
       <c r="U2">
         <f>Derivation!U6</f>
-        <v>0.999</v>
+        <v>0.99897998885348638</v>
       </c>
       <c r="V2">
         <f>Derivation!V6</f>
